--- a/Supplemental Files/Table S3.xlsx
+++ b/Supplemental Files/Table S3.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Šimon Pavlů\Desktop\2. Differencial analysis of barley promoterome\Supplement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A787A07-B159-48D1-B6E8-8FB1D0F8AA98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36534AE7-E08A-4ACC-A65A-9A2D32E26C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -723,22 +723,22 @@
         <v>7</v>
       </c>
       <c r="B3" s="5">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="C3" s="5">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="D3" s="5">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="E3" s="6">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="F3" s="6">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G3" s="6">
-        <v>229</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -746,22 +746,22 @@
         <v>8</v>
       </c>
       <c r="B4" s="5">
-        <v>334</v>
+        <v>297</v>
       </c>
       <c r="C4" s="5">
-        <v>397</v>
+        <v>338</v>
       </c>
       <c r="D4" s="5">
-        <v>356</v>
+        <v>303</v>
       </c>
       <c r="E4" s="5">
-        <v>382</v>
+        <v>319</v>
       </c>
       <c r="F4" s="5">
-        <v>328</v>
+        <v>290</v>
       </c>
       <c r="G4" s="5">
-        <v>400</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
@@ -769,22 +769,22 @@
         <v>9</v>
       </c>
       <c r="B5" s="6">
+        <v>146</v>
+      </c>
+      <c r="C5" s="6">
+        <v>156</v>
+      </c>
+      <c r="D5" s="6">
+        <v>136</v>
+      </c>
+      <c r="E5" s="6">
+        <v>152</v>
+      </c>
+      <c r="F5" s="6">
+        <v>143</v>
+      </c>
+      <c r="G5" s="6">
         <v>169</v>
-      </c>
-      <c r="C5" s="6">
-        <v>181</v>
-      </c>
-      <c r="D5" s="6">
-        <v>162</v>
-      </c>
-      <c r="E5" s="6">
-        <v>182</v>
-      </c>
-      <c r="F5" s="6">
-        <v>174</v>
-      </c>
-      <c r="G5" s="6">
-        <v>206</v>
       </c>
     </row>
   </sheetData>

--- a/Supplemental Files/Table S3.xlsx
+++ b/Supplemental Files/Table S3.xlsx
@@ -5,27 +5,38 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Šimon Pavlů\Desktop\2. Differencial analysis of barley promoterome\Supplement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Šimon Pavlů\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36534AE7-E08A-4ACC-A65A-9A2D32E26C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D16B28E7-E7A6-404B-A87B-DDA10AACB535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>Dataset</t>
   </si>
@@ -51,20 +62,53 @@
     <t>TATAxTATA</t>
   </si>
   <si>
-    <t>TATAxnonTATA</t>
-  </si>
-  <si>
-    <t>nonTATAxnonTATA</t>
-  </si>
-  <si>
-    <t>TableS3 - Number of long shifts between samples, categorized based on the presence or absence of TATA-box motif in the upstream regions of shifting TSSs</t>
+    <t>TableS3A - Number of long shifts between samples, categorized based on the presence or absence of TATA-box motif in the upstream regions of shifting TSSs</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TableS3B - Number of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>unique</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> long shifts per gene (unique shifts differ in at least one of the shifting TSS locations, hence the TATA-box presence might change)</t>
+    </r>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>TATAxTATAless</t>
+  </si>
+  <si>
+    <t>TATAlessxTATAless</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -76,6 +120,15 @@
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -173,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -181,11 +234,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="19">
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -346,23 +400,157 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -400,7 +588,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FF5395E5-B4A4-4778-97E4-C989B5A4B1EA}" name="Tabulka1" displayName="Tabulka1" ref="A2:G5" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FF5395E5-B4A4-4778-97E4-C989B5A4B1EA}" name="Tabulka1" displayName="Tabulka1" ref="A2:G5" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
   <autoFilter ref="A2:G5" xr:uid="{FF5395E5-B4A4-4778-97E4-C989B5A4B1EA}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{55A74C76-9995-40D1-897A-03119A8BB5C3}" name="Dataset" dataDxfId="6"/>
@@ -410,6 +598,19 @@
     <tableColumn id="2" xr3:uid="{D16DF18A-B9F9-4D5B-8C2A-99067EFA81B5}" name="8DAPxINF" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{56E1EAEE-BFC5-4CD6-8BAA-C676A6B074BB}" name="24DAPxINF" dataDxfId="1"/>
     <tableColumn id="4" xr3:uid="{BCF8AFE1-87DC-4877-96DE-9384D3631B7B}" name="4DAGxINF" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5135F6-47C6-4F1D-AB67-C984EEF8E261}" name="Tabulka14" displayName="Tabulka14" ref="A9:D10" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="16" tableBorderDxfId="17" totalsRowBorderDxfId="15">
+  <autoFilter ref="A9:D10" xr:uid="{CA5135F6-47C6-4F1D-AB67-C984EEF8E261}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{0EF8FA16-B462-4E63-94A2-8CBDA63A3F8B}" name=" " dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{253C3C3B-4139-49ED-8C55-DC4B5224BF54}" name="TATAxTATA" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{3D4BA074-F54C-4E70-B409-E3D34634B585}" name="TATAxTATAless" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{E50E6742-CDD4-4640-8D93-78B4903FCF77}" name="TATAlessxTATAless" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -678,13 +879,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.44140625" customWidth="1"/>
     <col min="2" max="2" width="14.44140625" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" customWidth="1"/>
     <col min="5" max="5" width="14.44140625" customWidth="1"/>
     <col min="6" max="6" width="13.33203125" customWidth="1"/>
     <col min="7" max="7" width="14.5546875" customWidth="1"/>
@@ -692,7 +893,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -743,7 +944,7 @@
     </row>
     <row r="4" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B4" s="5">
         <v>297</v>
@@ -766,7 +967,7 @@
     </row>
     <row r="5" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B5" s="6">
         <v>146</v>
@@ -787,11 +988,47 @@
         <v>169</v>
       </c>
     </row>
+    <row r="8" spans="1:7" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5">
+        <v>580</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1015</v>
+      </c>
+      <c r="D10" s="5">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Supplemental Files/Table S3.xlsx
+++ b/Supplemental Files/Table S3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Šimon Pavlů\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Šimon Pavlů\Desktop\2. Differencial analysis of barley promoterome\Supplement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D16B28E7-E7A6-404B-A87B-DDA10AACB535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADD77393-97FB-4548-96E1-C22AF507F408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,33 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
-  <si>
-    <t>Dataset</t>
-  </si>
-  <si>
-    <t>4DAGx24DAP</t>
-  </si>
-  <si>
-    <t>4DAGx8DAP</t>
-  </si>
-  <si>
-    <t>24DAPx8DAP</t>
-  </si>
-  <si>
-    <t>8DAPxINF</t>
-  </si>
-  <si>
-    <t>24DAPxINF</t>
-  </si>
-  <si>
-    <t>4DAGxINF</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>TATAxTATA</t>
-  </si>
-  <si>
-    <t>TableS3A - Number of long shifts between samples, categorized based on the presence or absence of TATA-box motif in the upstream regions of shifting TSSs</t>
   </si>
   <si>
     <r>
@@ -140,7 +116,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -209,103 +185,22 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -400,13 +295,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -423,134 +311,7 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
       <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -588,29 +349,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FF5395E5-B4A4-4778-97E4-C989B5A4B1EA}" name="Tabulka1" displayName="Tabulka1" ref="A2:G5" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
-  <autoFilter ref="A2:G5" xr:uid="{FF5395E5-B4A4-4778-97E4-C989B5A4B1EA}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{55A74C76-9995-40D1-897A-03119A8BB5C3}" name="Dataset" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{74E46096-9FB1-4FDA-A932-8755E97A6785}" name="4DAGx24DAP" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{308B2A84-B0D5-45CE-88A5-0E54865761C9}" name="4DAGx8DAP" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{A8BBC836-EE97-44D0-AAB7-D99007FC5765}" name="24DAPx8DAP" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{D16DF18A-B9F9-4D5B-8C2A-99067EFA81B5}" name="8DAPxINF" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{56E1EAEE-BFC5-4CD6-8BAA-C676A6B074BB}" name="24DAPxINF" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{BCF8AFE1-87DC-4877-96DE-9384D3631B7B}" name="4DAGxINF" dataDxfId="0"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5135F6-47C6-4F1D-AB67-C984EEF8E261}" name="Tabulka14" displayName="Tabulka14" ref="A9:D10" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="16" tableBorderDxfId="17" totalsRowBorderDxfId="15">
-  <autoFilter ref="A9:D10" xr:uid="{CA5135F6-47C6-4F1D-AB67-C984EEF8E261}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5135F6-47C6-4F1D-AB67-C984EEF8E261}" name="Tabulka14" displayName="Tabulka14" ref="A2:D3" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
+  <autoFilter ref="A2:D3" xr:uid="{CA5135F6-47C6-4F1D-AB67-C984EEF8E261}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0EF8FA16-B462-4E63-94A2-8CBDA63A3F8B}" name=" " dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{253C3C3B-4139-49ED-8C55-DC4B5224BF54}" name="TATAxTATA" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{3D4BA074-F54C-4E70-B409-E3D34634B585}" name="TATAxTATAless" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{E50E6742-CDD4-4640-8D93-78B4903FCF77}" name="TATAlessxTATAless" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{0EF8FA16-B462-4E63-94A2-8CBDA63A3F8B}" name=" " dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{253C3C3B-4139-49ED-8C55-DC4B5224BF54}" name="TATAxTATA" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{3D4BA074-F54C-4E70-B409-E3D34634B585}" name="TATAxTATAless" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{E50E6742-CDD4-4640-8D93-78B4903FCF77}" name="TATAlessxTATAless" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -879,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.44140625" customWidth="1"/>
@@ -891,144 +636,46 @@
     <col min="7" max="7" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>6</v>
+      <c r="B3" s="4">
+        <v>580</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1015</v>
+      </c>
+      <c r="D3" s="4">
+        <v>536</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="5">
-        <v>175</v>
-      </c>
-      <c r="C3" s="5">
-        <v>225</v>
-      </c>
-      <c r="D3" s="5">
-        <v>163</v>
-      </c>
-      <c r="E3" s="6">
-        <v>160</v>
-      </c>
-      <c r="F3" s="6">
-        <v>164</v>
-      </c>
-      <c r="G3" s="6">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="5">
-        <v>297</v>
-      </c>
-      <c r="C4" s="5">
-        <v>338</v>
-      </c>
-      <c r="D4" s="5">
-        <v>303</v>
-      </c>
-      <c r="E4" s="5">
-        <v>319</v>
-      </c>
-      <c r="F4" s="5">
-        <v>290</v>
-      </c>
-      <c r="G4" s="5">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="6">
-        <v>146</v>
-      </c>
-      <c r="C5" s="6">
-        <v>156</v>
-      </c>
-      <c r="D5" s="6">
-        <v>136</v>
-      </c>
-      <c r="E5" s="6">
-        <v>152</v>
-      </c>
-      <c r="F5" s="6">
-        <v>143</v>
-      </c>
-      <c r="G5" s="6">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="5">
-        <v>580</v>
-      </c>
-      <c r="C10" s="5">
-        <v>1015</v>
-      </c>
-      <c r="D10" s="5">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:4" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:4" ht="13.8" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="2">
+  <tableParts count="1">
     <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Supplemental Files/Table S3.xlsx
+++ b/Supplemental Files/Table S3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Šimon Pavlů\Desktop\2. Differencial analysis of barley promoterome\Supplement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADD77393-97FB-4548-96E1-C22AF507F408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F186714-BA58-48C4-8D44-2886A47CB28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -660,13 +660,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>580</v>
+        <v>19</v>
       </c>
       <c r="C3" s="4">
-        <v>1015</v>
+        <v>305</v>
       </c>
       <c r="D3" s="4">
-        <v>536</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/Supplemental Files/Table S3.xlsx
+++ b/Supplemental Files/Table S3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Šimon Pavlů\Desktop\2. Differencial analysis of barley promoterome\Supplement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E350E363-7DD8-4D00-B9FE-0317453D4738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E574E28-CA8F-4763-820B-A1954658C5A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3346,7 +3346,7 @@
         <family val="2"/>
         <charset val="238"/>
       </rPr>
-      <t>Table S4</t>
+      <t>Table S3</t>
     </r>
     <r>
       <rPr>
